--- a/A_C.xlsx
+++ b/A_C.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://leeds365-my.sharepoint.com/personal/tsaar_leeds_ac_uk/Documents/Mortezapour/Anthropomorphism and trust in AVs/Meta-analysis/Analyses/GitHub/Anthro_Control/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1366" documentId="13_ncr:1_{F8136FD0-F4F1-4E58-9F0C-F8C3DE43D527}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FDCEF271-442F-4B91-8D7F-693FB42789D6}"/>
+  <xr:revisionPtr revIDLastSave="1372" documentId="13_ncr:1_{F8136FD0-F4F1-4E58-9F0C-F8C3DE43D527}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A2EFD8B8-A424-4498-8D26-5226D1BAEE32}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B6800746-0385-4393-B9ED-EC356D81BE11}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="212">
   <si>
     <t>RoB_Score</t>
   </si>
@@ -663,6 +663,15 @@
   </si>
   <si>
     <t>Anthropomorphism_Modality</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cultural_Differences </t>
+  </si>
+  <si>
+    <t>Western</t>
+  </si>
+  <si>
+    <t>Eastern</t>
   </si>
 </sst>
 </file>
@@ -743,7 +752,45 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="57">
+  <dxfs count="59">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1840,45 +1887,42 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C3D885CD-7EC7-4014-AFAB-918F79E7B87B}" name="Table1" displayName="Table1" ref="A1:AB35" totalsRowShown="0" headerRowDxfId="56" dataDxfId="55">
-  <autoFilter ref="A1:AB35" xr:uid="{C3D885CD-7EC7-4014-AFAB-918F79E7B87B}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AB35">
-    <sortCondition ref="H1:H35"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C3D885CD-7EC7-4014-AFAB-918F79E7B87B}" name="Table1" displayName="Table1" ref="A1:AC35" totalsRowShown="0" headerRowDxfId="58" dataDxfId="57">
+  <autoFilter ref="A1:AC35" xr:uid="{C3D885CD-7EC7-4014-AFAB-918F79E7B87B}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AC35">
+    <sortCondition ref="I1:I35"/>
   </sortState>
-  <tableColumns count="28">
-    <tableColumn id="57" xr3:uid="{6C849D87-2A1C-44AF-8D60-342EC5E291CC}" name="Country" dataDxfId="54" totalsRowDxfId="53"/>
-    <tableColumn id="56" xr3:uid="{147DE22C-0ECD-4427-AD04-138D6595E7D8}" name="Continent" dataDxfId="52" totalsRowDxfId="51"/>
-    <tableColumn id="5" xr3:uid="{06FA886B-B664-408C-B99D-C8F03DED5941}" name="RoB_Score" dataDxfId="50" totalsRowDxfId="49"/>
-    <tableColumn id="55" xr3:uid="{279B8875-EC60-4313-94EB-821C0044F962}" name="JBI_Percentage" dataDxfId="48" totalsRowDxfId="47"/>
-    <tableColumn id="58" xr3:uid="{68E1FEFB-5918-4605-AE77-7B5A6BD98BA0}" name="JBI_Quality" dataDxfId="46" totalsRowDxfId="45"/>
-    <tableColumn id="7" xr3:uid="{1BC4C33B-D65E-4522-9BDC-575B3B59F8CA}" name="Study_Type" dataDxfId="44" totalsRowDxfId="43"/>
-    <tableColumn id="62" xr3:uid="{05813507-1144-45E4-AA51-AAD64C0F6D09}" name="Study_ID" dataDxfId="42" totalsRowDxfId="41"/>
-    <tableColumn id="8" xr3:uid="{E638A864-4A49-481F-84A1-215079EEFFAF}" name="first Author" dataDxfId="40" totalsRowDxfId="39"/>
-    <tableColumn id="9" xr3:uid="{C7F609F4-33E0-48D2-B769-C787CA2CEE6A}" name="Publication_Date" dataDxfId="38" totalsRowDxfId="37"/>
-    <tableColumn id="10" xr3:uid="{70217497-0503-44AD-943C-B30943C185B5}" name="study Design" dataDxfId="36" totalsRowDxfId="35"/>
-    <tableColumn id="11" xr3:uid="{AB30B7D5-2F37-49BA-856B-09BF64B20B7A}" name="sample Size" dataDxfId="34" totalsRowDxfId="33"/>
-    <tableColumn id="12" xr3:uid="{95F223F0-7A1C-418C-AAF6-979C672568D3}" name="age: Year (SD); min/max; [P25, Median, P75]" dataDxfId="32" totalsRowDxfId="31"/>
-    <tableColumn id="59" xr3:uid="{D1E873D0-2299-4CC5-909D-C73519EF23AF}" name="Age_Average" dataDxfId="30" totalsRowDxfId="29"/>
-    <tableColumn id="16" xr3:uid="{45CE4031-9F11-431E-AAC8-65A108B5DB21}" name="gender: Female (No / %); Male (No / %)" dataDxfId="28" totalsRowDxfId="27"/>
-    <tableColumn id="60" xr3:uid="{90990895-4B83-475F-A5CE-CAA11C0B97B4}" name="Female_Percentage" dataDxfId="26" totalsRowDxfId="25"/>
-    <tableColumn id="28" xr3:uid="{BB9C0C78-E4BE-4021-96C7-94790A827A4E}" name="Trust measurement tool (Objective (specify), Questionnaire (specify), Interview, Other)" dataDxfId="24" totalsRowDxfId="23"/>
-    <tableColumn id="33" xr3:uid="{E41C6D12-2DB0-4F29-8E48-BB3FE4AC2A7B}" name="Anthropomorphism_Modality" dataDxfId="22" totalsRowDxfId="21"/>
-    <tableColumn id="34" xr3:uid="{7F6E03AB-90AD-4F70-BA48-002F9D4247AB}" name="N_A" dataDxfId="20" totalsRowDxfId="19"/>
-    <tableColumn id="35" xr3:uid="{684C62BB-7A6F-4F6F-A898-77142C4CC598}" name="M_A" dataDxfId="18" totalsRowDxfId="17"/>
-    <tableColumn id="36" xr3:uid="{577A89CB-8F11-4E3C-823D-A93E5E8A0EB9}" name="SD_A" dataDxfId="16" totalsRowDxfId="15"/>
-    <tableColumn id="37" xr3:uid="{86232F69-E61C-4615-9197-93D22266E960}" name="comparison_Modality" dataDxfId="14" totalsRowDxfId="13"/>
-    <tableColumn id="38" xr3:uid="{8C2F558E-2E10-4E3E-9D6E-78943CA7E74E}" name="N_C" dataDxfId="12" totalsRowDxfId="11"/>
-    <tableColumn id="39" xr3:uid="{DEF956DF-ECE7-477C-B690-61CB8122DE47}" name="M_C" dataDxfId="10" totalsRowDxfId="9"/>
-    <tableColumn id="40" xr3:uid="{424FE405-38CB-4ACC-8F2C-712CCAD9D5B9}" name="SD_C" dataDxfId="8" totalsRowDxfId="7"/>
-    <tableColumn id="46" xr3:uid="{958E3012-F6ED-4652-93CC-5EFFCE02F2C9}" name="Automation_Level" dataDxfId="6" totalsRowDxfId="5"/>
-    <tableColumn id="47" xr3:uid="{CB92076A-76AE-4A3C-B528-84ED8789CE81}" name="Participant_Role" dataDxfId="4"/>
-    <tableColumn id="61" xr3:uid="{3C6B633F-427A-47AC-8033-31F86637F84B}" name="Driving_Simulation" dataDxfId="3" totalsRowDxfId="2"/>
-    <tableColumn id="49" xr3:uid="{BE070A8C-ABF2-4217-BE7E-8631C27686FD}" name="NDRT" dataDxfId="1" totalsRowDxfId="0"/>
+  <tableColumns count="29">
+    <tableColumn id="57" xr3:uid="{6C849D87-2A1C-44AF-8D60-342EC5E291CC}" name="Country" dataDxfId="56" totalsRowDxfId="55"/>
+    <tableColumn id="56" xr3:uid="{147DE22C-0ECD-4427-AD04-138D6595E7D8}" name="Continent" dataDxfId="54" totalsRowDxfId="53"/>
+    <tableColumn id="5" xr3:uid="{06FA886B-B664-408C-B99D-C8F03DED5941}" name="RoB_Score" dataDxfId="52" totalsRowDxfId="51"/>
+    <tableColumn id="55" xr3:uid="{279B8875-EC60-4313-94EB-821C0044F962}" name="JBI_Percentage" dataDxfId="50" totalsRowDxfId="49"/>
+    <tableColumn id="58" xr3:uid="{68E1FEFB-5918-4605-AE77-7B5A6BD98BA0}" name="JBI_Quality" dataDxfId="48" totalsRowDxfId="47"/>
+    <tableColumn id="7" xr3:uid="{1BC4C33B-D65E-4522-9BDC-575B3B59F8CA}" name="Study_Type" dataDxfId="46" totalsRowDxfId="45"/>
+    <tableColumn id="62" xr3:uid="{05813507-1144-45E4-AA51-AAD64C0F6D09}" name="Study_ID" dataDxfId="44" totalsRowDxfId="43"/>
+    <tableColumn id="1" xr3:uid="{D8D78711-68BA-4FC8-ABB2-BAEADD7E34E4}" name="Cultural_Differences " dataDxfId="0" totalsRowDxfId="1"/>
+    <tableColumn id="8" xr3:uid="{E638A864-4A49-481F-84A1-215079EEFFAF}" name="first Author" dataDxfId="42" totalsRowDxfId="41"/>
+    <tableColumn id="9" xr3:uid="{C7F609F4-33E0-48D2-B769-C787CA2CEE6A}" name="Publication_Date" dataDxfId="40" totalsRowDxfId="39"/>
+    <tableColumn id="10" xr3:uid="{70217497-0503-44AD-943C-B30943C185B5}" name="study Design" dataDxfId="38" totalsRowDxfId="37"/>
+    <tableColumn id="11" xr3:uid="{AB30B7D5-2F37-49BA-856B-09BF64B20B7A}" name="sample Size" dataDxfId="36" totalsRowDxfId="35"/>
+    <tableColumn id="12" xr3:uid="{95F223F0-7A1C-418C-AAF6-979C672568D3}" name="age: Year (SD); min/max; [P25, Median, P75]" dataDxfId="34" totalsRowDxfId="33"/>
+    <tableColumn id="59" xr3:uid="{D1E873D0-2299-4CC5-909D-C73519EF23AF}" name="Age_Average" dataDxfId="32" totalsRowDxfId="31"/>
+    <tableColumn id="16" xr3:uid="{45CE4031-9F11-431E-AAC8-65A108B5DB21}" name="gender: Female (No / %); Male (No / %)" dataDxfId="30" totalsRowDxfId="29"/>
+    <tableColumn id="60" xr3:uid="{90990895-4B83-475F-A5CE-CAA11C0B97B4}" name="Female_Percentage" dataDxfId="28" totalsRowDxfId="27"/>
+    <tableColumn id="28" xr3:uid="{BB9C0C78-E4BE-4021-96C7-94790A827A4E}" name="Trust measurement tool (Objective (specify), Questionnaire (specify), Interview, Other)" dataDxfId="26" totalsRowDxfId="25"/>
+    <tableColumn id="33" xr3:uid="{E41C6D12-2DB0-4F29-8E48-BB3FE4AC2A7B}" name="Anthropomorphism_Modality" dataDxfId="24" totalsRowDxfId="23"/>
+    <tableColumn id="34" xr3:uid="{7F6E03AB-90AD-4F70-BA48-002F9D4247AB}" name="N_A" dataDxfId="22" totalsRowDxfId="21"/>
+    <tableColumn id="35" xr3:uid="{684C62BB-7A6F-4F6F-A898-77142C4CC598}" name="M_A" dataDxfId="20" totalsRowDxfId="19"/>
+    <tableColumn id="36" xr3:uid="{577A89CB-8F11-4E3C-823D-A93E5E8A0EB9}" name="SD_A" dataDxfId="18" totalsRowDxfId="17"/>
+    <tableColumn id="37" xr3:uid="{86232F69-E61C-4615-9197-93D22266E960}" name="comparison_Modality" dataDxfId="16" totalsRowDxfId="15"/>
+    <tableColumn id="38" xr3:uid="{8C2F558E-2E10-4E3E-9D6E-78943CA7E74E}" name="N_C" dataDxfId="14" totalsRowDxfId="13"/>
+    <tableColumn id="39" xr3:uid="{DEF956DF-ECE7-477C-B690-61CB8122DE47}" name="M_C" dataDxfId="12" totalsRowDxfId="11"/>
+    <tableColumn id="40" xr3:uid="{424FE405-38CB-4ACC-8F2C-712CCAD9D5B9}" name="SD_C" dataDxfId="10" totalsRowDxfId="9"/>
+    <tableColumn id="46" xr3:uid="{958E3012-F6ED-4652-93CC-5EFFCE02F2C9}" name="Automation_Level" dataDxfId="8" totalsRowDxfId="7"/>
+    <tableColumn id="47" xr3:uid="{CB92076A-76AE-4A3C-B528-84ED8789CE81}" name="Participant_Role" dataDxfId="6"/>
+    <tableColumn id="61" xr3:uid="{3C6B633F-427A-47AC-8033-31F86637F84B}" name="Driving_Simulation" dataDxfId="5" totalsRowDxfId="4"/>
+    <tableColumn id="49" xr3:uid="{BE070A8C-ABF2-4217-BE7E-8631C27686FD}" name="NDRT" dataDxfId="3" totalsRowDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2181,7 +2225,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF9409AD-B1B7-497F-AA36-7339CA603B38}">
-  <dimension ref="A1:AB35"/>
+  <dimension ref="A1:AC35"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="10.109375" bestFit="1" customWidth="1"/>
@@ -2191,28 +2235,29 @@
     <col min="5" max="5" width="16" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.6640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.88671875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19.88671875" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="15.44140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.77734375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="33.44140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="22.109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="28.109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="24.6640625" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="21.77734375" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="20.109375" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="20.6640625" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="20.6640625" customWidth="1"/>
-    <col min="29" max="29" width="60.33203125" customWidth="1"/>
+    <col min="8" max="8" width="20.21875" customWidth="1"/>
+    <col min="9" max="9" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="33.44140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="22.109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="28.109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="24.6640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="21.77734375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="20.109375" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="20.6640625" customWidth="1"/>
+    <col min="30" max="30" width="60.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="82.8">
+    <row r="1" spans="1:29" ht="82.8">
       <c r="A1" s="1" t="s">
         <v>117</v>
       </c>
@@ -2235,70 +2280,73 @@
         <v>207</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:28" ht="96" customHeight="1">
+    <row r="2" spans="1:29" ht="96" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>183</v>
       </c>
@@ -2321,68 +2369,71 @@
         <v>1</v>
       </c>
       <c r="H2" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2" s="1">
         <v>2024</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="K2" s="1">
+      <c r="L2" s="1">
         <v>28</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="M2" s="1">
+      <c r="N2" s="1">
         <v>27.2</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="O2" s="1">
+      <c r="P2" s="1">
         <v>18</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="Q2" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="R2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="R2" s="1">
+      <c r="S2" s="1">
         <v>28</v>
       </c>
-      <c r="S2" s="1">
+      <c r="T2" s="1">
         <v>4.58</v>
       </c>
-      <c r="T2" s="1">
+      <c r="U2" s="1">
         <v>1.58</v>
       </c>
-      <c r="U2" s="1" t="s">
+      <c r="V2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="V2" s="1">
+      <c r="W2" s="1">
         <v>28</v>
       </c>
-      <c r="W2" s="1">
+      <c r="X2" s="1">
         <v>4.78</v>
       </c>
-      <c r="X2" s="1">
+      <c r="Y2" s="1">
         <v>1.58</v>
       </c>
-      <c r="Y2" s="1" t="s">
+      <c r="Z2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Z2" s="1" t="s">
+      <c r="AA2" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="AA2" s="1" t="s">
+      <c r="AB2" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="AB2" s="1"/>
+      <c r="AC2" s="1"/>
     </row>
-    <row r="3" spans="1:28" ht="37.950000000000003" customHeight="1">
+    <row r="3" spans="1:29" ht="37.950000000000003" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>178</v>
       </c>
@@ -2405,70 +2456,73 @@
         <v>2</v>
       </c>
       <c r="H3" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="I3" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3" s="1">
         <v>2018</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="K3" s="1">
+      <c r="L3" s="1">
         <v>23</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="M3" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="M3" s="1">
+      <c r="N3" s="1">
         <v>28.7</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="O3" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="O3" s="1">
+      <c r="P3" s="1">
         <v>17</v>
       </c>
-      <c r="P3" s="1" t="s">
+      <c r="Q3" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="Q3" s="1" t="s">
+      <c r="R3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="R3" s="1">
+      <c r="S3" s="1">
         <v>23</v>
       </c>
-      <c r="S3" s="1">
+      <c r="T3" s="1">
         <v>4.3099999999999996</v>
       </c>
-      <c r="T3" s="1">
+      <c r="U3" s="1">
         <v>1.22</v>
       </c>
-      <c r="U3" s="1" t="s">
+      <c r="V3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="V3" s="1">
+      <c r="W3" s="1">
         <v>23</v>
       </c>
-      <c r="W3" s="1">
+      <c r="X3" s="1">
         <v>3.45</v>
       </c>
-      <c r="X3" s="1">
+      <c r="Y3" s="1">
         <v>1.23</v>
       </c>
-      <c r="Y3" s="1" t="s">
+      <c r="Z3" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="Z3" s="1" t="s">
+      <c r="AA3" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AA3" s="1" t="s">
+      <c r="AB3" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="AB3" s="1" t="s">
+      <c r="AC3" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:28" ht="41.4">
+    <row r="4" spans="1:29" ht="41.4">
       <c r="A4" s="1" t="s">
         <v>185</v>
       </c>
@@ -2491,70 +2545,73 @@
         <v>3</v>
       </c>
       <c r="H4" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="I4" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4" s="1">
         <v>2019</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="K4" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="K4" s="1">
+      <c r="L4" s="1">
         <v>11</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="M4" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="M4" s="1">
+      <c r="N4" s="1">
         <v>47</v>
       </c>
-      <c r="N4" s="1" t="s">
+      <c r="O4" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="O4" s="1">
+      <c r="P4" s="1">
         <v>45</v>
       </c>
-      <c r="P4" s="1" t="s">
+      <c r="Q4" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="Q4" s="1" t="s">
+      <c r="R4" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="R4" s="1">
+      <c r="S4" s="1">
         <v>11</v>
       </c>
-      <c r="S4" s="1">
+      <c r="T4" s="1">
         <v>5.0599999999999996</v>
       </c>
-      <c r="T4" s="1">
+      <c r="U4" s="1">
         <v>1.19</v>
       </c>
-      <c r="U4" s="1" t="s">
+      <c r="V4" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="V4" s="1">
+      <c r="W4" s="1">
         <v>11</v>
       </c>
-      <c r="W4" s="1">
+      <c r="X4" s="1">
         <v>5.12</v>
       </c>
-      <c r="X4" s="1">
+      <c r="Y4" s="1">
         <v>1.51</v>
       </c>
-      <c r="Y4" s="1" t="s">
+      <c r="Z4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Z4" s="1" t="s">
+      <c r="AA4" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AA4" s="1" t="s">
+      <c r="AB4" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="AB4" s="1" t="s">
+      <c r="AC4" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:28" ht="27.6">
+    <row r="5" spans="1:29" ht="27.6">
       <c r="A5" s="1" t="s">
         <v>181</v>
       </c>
@@ -2577,68 +2634,71 @@
         <v>5</v>
       </c>
       <c r="H5" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="I5" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5" s="1">
         <v>2023</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="K5" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="K5" s="1">
+      <c r="L5" s="1">
         <v>731</v>
       </c>
-      <c r="L5" s="1" t="s">
+      <c r="M5" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="M5" s="1">
+      <c r="N5" s="1">
         <v>41.58</v>
       </c>
-      <c r="N5" s="1" t="s">
+      <c r="O5" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="O5" s="1">
+      <c r="P5" s="1">
         <v>52</v>
       </c>
-      <c r="P5" s="1" t="s">
+      <c r="Q5" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="Q5" s="1" t="s">
+      <c r="R5" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="R5" s="1">
+      <c r="S5" s="1">
         <v>731</v>
       </c>
-      <c r="S5" s="1">
+      <c r="T5" s="1">
         <v>4</v>
       </c>
-      <c r="T5" s="1">
+      <c r="U5" s="1">
         <v>1.26</v>
       </c>
-      <c r="U5" s="1" t="s">
+      <c r="V5" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="V5" s="1">
+      <c r="W5" s="1">
         <v>731</v>
       </c>
-      <c r="W5" s="1">
+      <c r="X5" s="1">
         <v>3.88</v>
       </c>
-      <c r="X5" s="1">
+      <c r="Y5" s="1">
         <v>1.26</v>
       </c>
-      <c r="Y5" s="1" t="s">
+      <c r="Z5" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="Z5" s="1" t="s">
+      <c r="AA5" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="AA5" s="1" t="s">
+      <c r="AB5" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="AB5" s="1"/>
+      <c r="AC5" s="1"/>
     </row>
-    <row r="6" spans="1:28" ht="41.4">
+    <row r="6" spans="1:29" ht="41.4">
       <c r="A6" s="1" t="s">
         <v>177</v>
       </c>
@@ -2660,69 +2720,72 @@
       <c r="G6" s="1">
         <v>6</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="H6" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6" s="1">
         <v>2022</v>
       </c>
-      <c r="J6" s="1" t="s">
+      <c r="K6" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="K6" s="1">
+      <c r="L6" s="1">
         <v>45</v>
       </c>
-      <c r="L6" s="1" t="s">
+      <c r="M6" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="M6" s="1">
+      <c r="N6" s="1">
         <v>23</v>
       </c>
-      <c r="N6" s="1" t="s">
+      <c r="O6" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="O6" s="1">
+      <c r="P6" s="1">
         <v>64</v>
       </c>
-      <c r="P6" s="1" t="s">
+      <c r="Q6" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="Q6" s="1" t="s">
+      <c r="R6" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="R6" s="1">
+      <c r="S6" s="1">
         <v>45</v>
       </c>
-      <c r="S6" s="1">
+      <c r="T6" s="1">
         <v>5.24</v>
       </c>
-      <c r="T6" s="1">
+      <c r="U6" s="1">
         <v>0.3</v>
       </c>
-      <c r="U6" s="1" t="s">
+      <c r="V6" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="V6" s="1">
+      <c r="W6" s="1">
         <v>45</v>
       </c>
-      <c r="W6" s="1">
+      <c r="X6" s="1">
         <v>5.15</v>
       </c>
-      <c r="X6" s="1">
+      <c r="Y6" s="1">
         <v>0.3</v>
       </c>
-      <c r="Y6" s="1" t="s">
+      <c r="Z6" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Z6" s="1" t="s">
+      <c r="AA6" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="AA6" s="1" t="s">
+      <c r="AB6" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="AB6" s="1"/>
+      <c r="AC6" s="1"/>
     </row>
-    <row r="7" spans="1:28" ht="27.6">
+    <row r="7" spans="1:29" ht="27.6">
       <c r="A7" s="1" t="s">
         <v>177</v>
       </c>
@@ -2745,68 +2808,71 @@
         <v>7</v>
       </c>
       <c r="H7" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="I7" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7" s="1">
         <v>2024</v>
       </c>
-      <c r="J7" s="1" t="s">
+      <c r="K7" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="K7" s="1">
+      <c r="L7" s="1">
         <v>38</v>
       </c>
-      <c r="L7" s="1" t="s">
+      <c r="M7" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="M7" s="1">
+      <c r="N7" s="1">
         <v>10.73</v>
       </c>
-      <c r="N7" s="1" t="s">
+      <c r="O7" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="O7" s="1">
+      <c r="P7" s="1">
         <v>34</v>
       </c>
-      <c r="P7" s="1" t="s">
+      <c r="Q7" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="Q7" s="1" t="s">
+      <c r="R7" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="R7" s="1">
+      <c r="S7" s="1">
         <v>38</v>
       </c>
-      <c r="S7" s="1">
+      <c r="T7" s="1">
         <v>1.97</v>
       </c>
-      <c r="T7" s="1">
+      <c r="U7" s="1">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="U7" s="1" t="s">
+      <c r="V7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="V7" s="1">
+      <c r="W7" s="1">
         <v>38</v>
       </c>
-      <c r="W7" s="1">
+      <c r="X7" s="1">
         <v>2.25</v>
       </c>
-      <c r="X7" s="1">
+      <c r="Y7" s="1">
         <v>0.08</v>
       </c>
-      <c r="Y7" s="1" t="s">
+      <c r="Z7" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Z7" s="1" t="s">
+      <c r="AA7" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="AA7" s="1" t="s">
+      <c r="AB7" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="AB7" s="1"/>
+      <c r="AC7" s="1"/>
     </row>
-    <row r="8" spans="1:28" ht="79.2" customHeight="1">
+    <row r="8" spans="1:29" ht="79.2" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>179</v>
       </c>
@@ -2829,70 +2895,73 @@
         <v>8</v>
       </c>
       <c r="H8" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="I8" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="I8" s="1">
+      <c r="J8" s="1">
         <v>2022</v>
       </c>
-      <c r="J8" s="1" t="s">
+      <c r="K8" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="K8" s="1">
+      <c r="L8" s="1">
         <v>226</v>
       </c>
-      <c r="L8" s="1" t="s">
+      <c r="M8" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="M8" s="1">
+      <c r="N8" s="1">
         <v>31.04</v>
       </c>
-      <c r="N8" s="1" t="s">
+      <c r="O8" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="O8" s="1">
+      <c r="P8" s="1">
         <v>42</v>
       </c>
-      <c r="P8" s="1" t="s">
+      <c r="Q8" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="Q8" s="1" t="s">
+      <c r="R8" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="R8" s="1">
+      <c r="S8" s="1">
         <v>20</v>
       </c>
-      <c r="S8" s="1">
+      <c r="T8" s="1">
         <v>3.47</v>
       </c>
-      <c r="T8" s="1">
+      <c r="U8" s="1">
         <v>0.8</v>
       </c>
-      <c r="U8" s="1" t="s">
+      <c r="V8" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="V8" s="1">
+      <c r="W8" s="1">
         <v>25</v>
       </c>
-      <c r="W8" s="1">
+      <c r="X8" s="1">
         <v>3.45</v>
       </c>
-      <c r="X8" s="1">
+      <c r="Y8" s="1">
         <v>0.79</v>
       </c>
-      <c r="Y8" s="1" t="s">
+      <c r="Z8" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Z8" s="1" t="s">
+      <c r="AA8" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AA8" s="1" t="s">
+      <c r="AB8" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="AB8" s="1" t="s">
+      <c r="AC8" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:28" ht="73.95" customHeight="1">
+    <row r="9" spans="1:29" ht="73.95" customHeight="1">
       <c r="A9" s="1" t="s">
         <v>179</v>
       </c>
@@ -2915,68 +2984,71 @@
         <v>10</v>
       </c>
       <c r="H9" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="I9" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="I9" s="1">
+      <c r="J9" s="1">
         <v>2020</v>
       </c>
-      <c r="J9" s="1" t="s">
+      <c r="K9" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="K9" s="1">
+      <c r="L9" s="1">
         <v>59</v>
       </c>
-      <c r="L9" s="1" t="s">
+      <c r="M9" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="M9" s="1">
+      <c r="N9" s="1">
         <v>42.98</v>
       </c>
-      <c r="N9" s="1" t="s">
+      <c r="O9" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="O9" s="1">
+      <c r="P9" s="1">
         <v>46</v>
       </c>
-      <c r="P9" s="1" t="s">
+      <c r="Q9" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="Q9" s="1" t="s">
+      <c r="R9" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="R9" s="1">
+      <c r="S9" s="1">
         <v>59</v>
       </c>
-      <c r="S9" s="1">
+      <c r="T9" s="1">
         <v>2.77</v>
       </c>
-      <c r="T9" s="1">
+      <c r="U9" s="1">
         <v>1.84</v>
       </c>
-      <c r="U9" s="1" t="s">
+      <c r="V9" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="V9" s="1">
+      <c r="W9" s="1">
         <v>59</v>
       </c>
-      <c r="W9" s="1">
+      <c r="X9" s="1">
         <v>2.23</v>
       </c>
-      <c r="X9" s="1">
+      <c r="Y9" s="1">
         <v>1.92</v>
       </c>
-      <c r="Y9" s="1" t="s">
+      <c r="Z9" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="Z9" s="1" t="s">
+      <c r="AA9" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="AA9" s="1" t="s">
+      <c r="AB9" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="AB9" s="1"/>
+      <c r="AC9" s="1"/>
     </row>
-    <row r="10" spans="1:28" ht="55.2">
+    <row r="10" spans="1:29" ht="41.4">
       <c r="A10" s="1" t="s">
         <v>179</v>
       </c>
@@ -2999,70 +3071,73 @@
         <v>11</v>
       </c>
       <c r="H10" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="I10" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="I10" s="1">
+      <c r="J10" s="1">
         <v>2021</v>
       </c>
-      <c r="J10" s="1" t="s">
+      <c r="K10" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="K10" s="1">
+      <c r="L10" s="1">
         <v>34</v>
       </c>
-      <c r="L10" s="1" t="s">
+      <c r="M10" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="M10" s="1">
+      <c r="N10" s="1">
         <v>29.9</v>
       </c>
-      <c r="N10" s="1" t="s">
+      <c r="O10" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="O10" s="1">
+      <c r="P10" s="1">
         <v>44</v>
       </c>
-      <c r="P10" s="1" t="s">
+      <c r="Q10" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="Q10" s="1" t="s">
+      <c r="R10" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="R10" s="1">
+      <c r="S10" s="1">
         <v>17</v>
       </c>
-      <c r="S10" s="1">
+      <c r="T10" s="1">
         <v>4</v>
       </c>
-      <c r="T10" s="1">
+      <c r="U10" s="1">
         <v>0.53</v>
       </c>
-      <c r="U10" s="1" t="s">
+      <c r="V10" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="V10" s="1">
+      <c r="W10" s="1">
         <v>17</v>
       </c>
-      <c r="W10" s="1">
+      <c r="X10" s="1">
         <v>4.45</v>
       </c>
-      <c r="X10" s="1">
+      <c r="Y10" s="1">
         <v>0.81</v>
       </c>
-      <c r="Y10" s="1" t="s">
+      <c r="Z10" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Z10" s="1" t="s">
+      <c r="AA10" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AA10" s="1" t="s">
+      <c r="AB10" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="AB10" s="1" t="s">
+      <c r="AC10" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:28" ht="54" customHeight="1">
+    <row r="11" spans="1:29" ht="54" customHeight="1">
       <c r="A11" s="1" t="s">
         <v>179</v>
       </c>
@@ -3085,70 +3160,73 @@
         <v>12</v>
       </c>
       <c r="H11" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="I11" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="I11" s="1">
+      <c r="J11" s="1">
         <v>2017</v>
       </c>
-      <c r="J11" s="1" t="s">
+      <c r="K11" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="K11" s="1">
+      <c r="L11" s="1">
         <v>17</v>
       </c>
-      <c r="L11" s="1" t="s">
+      <c r="M11" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M11" s="1">
+      <c r="N11" s="1">
         <v>29</v>
       </c>
-      <c r="N11" s="1" t="s">
+      <c r="O11" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="O11" s="1">
+      <c r="P11" s="1">
         <v>41</v>
       </c>
-      <c r="P11" s="1" t="s">
+      <c r="Q11" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="Q11" s="1" t="s">
+      <c r="R11" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="R11" s="1">
+      <c r="S11" s="1">
         <v>17</v>
       </c>
-      <c r="S11" s="1">
+      <c r="T11" s="1">
         <v>5.7</v>
       </c>
-      <c r="T11" s="1">
+      <c r="U11" s="1">
         <v>1.01</v>
       </c>
-      <c r="U11" s="1" t="s">
+      <c r="V11" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="V11" s="1">
+      <c r="W11" s="1">
         <v>17</v>
       </c>
-      <c r="W11" s="1">
+      <c r="X11" s="1">
         <v>5.27</v>
       </c>
-      <c r="X11" s="1">
+      <c r="Y11" s="1">
         <v>1.29</v>
       </c>
-      <c r="Y11" s="1" t="s">
+      <c r="Z11" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="Z11" s="1" t="s">
+      <c r="AA11" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AA11" s="1" t="s">
+      <c r="AB11" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="AB11" s="1" t="s">
+      <c r="AC11" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:28" ht="27.6">
+    <row r="12" spans="1:29" ht="27.6">
       <c r="A12" s="1" t="s">
         <v>179</v>
       </c>
@@ -3171,70 +3249,73 @@
         <v>13</v>
       </c>
       <c r="H12" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="I12" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="I12" s="1">
+      <c r="J12" s="1">
         <v>2019</v>
       </c>
-      <c r="J12" s="1" t="s">
+      <c r="K12" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="K12" s="1">
+      <c r="L12" s="1">
         <v>18</v>
       </c>
-      <c r="L12" s="1" t="s">
+      <c r="M12" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="M12" s="1">
+      <c r="N12" s="1">
         <v>25.11</v>
       </c>
-      <c r="N12" s="1" t="s">
+      <c r="O12" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="O12" s="1">
+      <c r="P12" s="1">
         <v>67</v>
       </c>
-      <c r="P12" s="1" t="s">
+      <c r="Q12" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="Q12" s="1" t="s">
+      <c r="R12" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="R12" s="1">
+      <c r="S12" s="1">
         <v>18</v>
       </c>
-      <c r="S12" s="1">
+      <c r="T12" s="1">
         <v>3.74</v>
       </c>
-      <c r="T12" s="1">
+      <c r="U12" s="1">
         <v>1.23</v>
       </c>
-      <c r="U12" s="1" t="s">
+      <c r="V12" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="V12" s="1">
+      <c r="W12" s="1">
         <v>18</v>
       </c>
-      <c r="W12" s="1">
+      <c r="X12" s="1">
         <v>3.25</v>
       </c>
-      <c r="X12" s="1">
+      <c r="Y12" s="1">
         <v>1.1299999999999999</v>
       </c>
-      <c r="Y12" s="1" t="s">
+      <c r="Z12" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="Z12" s="1" t="s">
+      <c r="AA12" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AA12" s="1" t="s">
+      <c r="AB12" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="AB12" s="1" t="s">
+      <c r="AC12" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:28" ht="58.2" customHeight="1">
+    <row r="13" spans="1:29" ht="58.2" customHeight="1">
       <c r="A13" s="1" t="s">
         <v>177</v>
       </c>
@@ -3257,70 +3338,73 @@
         <v>16</v>
       </c>
       <c r="H13" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="I13" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="I13" s="1">
+      <c r="J13" s="1">
         <v>2025</v>
       </c>
-      <c r="J13" s="1" t="s">
+      <c r="K13" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="K13" s="1">
+      <c r="L13" s="1">
         <v>70</v>
       </c>
-      <c r="L13" s="1" t="s">
+      <c r="M13" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="M13" s="1">
+      <c r="N13" s="1">
         <v>30.01</v>
       </c>
-      <c r="N13" s="1" t="s">
+      <c r="O13" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="O13" s="1">
+      <c r="P13" s="1">
         <v>47</v>
       </c>
-      <c r="P13" s="1" t="s">
+      <c r="Q13" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="Q13" s="1" t="s">
+      <c r="R13" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="R13" s="1">
+      <c r="S13" s="1">
         <v>9</v>
       </c>
-      <c r="S13" s="1">
+      <c r="T13" s="1">
         <v>4.75</v>
       </c>
-      <c r="T13" s="1">
+      <c r="U13" s="1">
         <v>1.05</v>
       </c>
-      <c r="U13" s="1" t="s">
+      <c r="V13" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="V13" s="1">
+      <c r="W13" s="1">
         <v>9</v>
       </c>
-      <c r="W13" s="1">
+      <c r="X13" s="1">
         <v>4.43</v>
       </c>
-      <c r="X13" s="1">
+      <c r="Y13" s="1">
         <v>0.81</v>
       </c>
-      <c r="Y13" s="1" t="s">
+      <c r="Z13" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Z13" s="1" t="s">
+      <c r="AA13" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AA13" s="1" t="s">
+      <c r="AB13" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="AB13" s="1" t="s">
+      <c r="AC13" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:28" ht="55.2">
+    <row r="14" spans="1:29" ht="55.2">
       <c r="A14" s="1" t="s">
         <v>122</v>
       </c>
@@ -3343,70 +3427,73 @@
         <v>23</v>
       </c>
       <c r="H14" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="I14" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="I14" s="1">
+      <c r="J14" s="1">
         <v>2022</v>
       </c>
-      <c r="J14" s="1" t="s">
+      <c r="K14" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="K14" s="1">
+      <c r="L14" s="1">
         <v>21</v>
       </c>
-      <c r="L14" s="1" t="s">
+      <c r="M14" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="M14" s="1">
+      <c r="N14" s="1">
         <v>19</v>
       </c>
-      <c r="N14" s="1" t="s">
+      <c r="O14" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="O14" s="1">
+      <c r="P14" s="1">
         <v>17</v>
       </c>
-      <c r="P14" s="1" t="s">
+      <c r="Q14" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="Q14" s="1" t="s">
+      <c r="R14" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="R14" s="1">
+      <c r="S14" s="1">
         <v>21</v>
       </c>
-      <c r="S14" s="1">
+      <c r="T14" s="1">
         <v>3.8</v>
       </c>
-      <c r="T14" s="1">
+      <c r="U14" s="1">
         <v>1.3</v>
       </c>
-      <c r="U14" s="1" t="s">
+      <c r="V14" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="V14" s="1">
+      <c r="W14" s="1">
         <v>21</v>
       </c>
-      <c r="W14" s="1">
+      <c r="X14" s="1">
         <v>4</v>
       </c>
-      <c r="X14" s="1">
+      <c r="Y14" s="1">
         <v>1.1000000000000001</v>
       </c>
-      <c r="Y14" s="1" t="s">
+      <c r="Z14" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="Z14" s="1" t="s">
+      <c r="AA14" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AA14" s="1" t="s">
+      <c r="AB14" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="AB14" s="1" t="s">
+      <c r="AC14" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:28" ht="27.6">
+    <row r="15" spans="1:29" ht="27.6">
       <c r="A15" s="1" t="s">
         <v>122</v>
       </c>
@@ -3428,71 +3515,74 @@
       <c r="G15" s="1">
         <v>24</v>
       </c>
-      <c r="H15" s="3" t="s">
+      <c r="H15" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="I15" s="1">
+      <c r="J15" s="1">
         <v>2018</v>
       </c>
-      <c r="J15" s="1" t="s">
+      <c r="K15" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="K15" s="1">
+      <c r="L15" s="1">
         <v>52</v>
       </c>
-      <c r="L15" s="1" t="s">
+      <c r="M15" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="M15" s="1">
+      <c r="N15" s="1">
         <v>37</v>
       </c>
-      <c r="N15" s="1" t="s">
+      <c r="O15" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="O15" s="1">
+      <c r="P15" s="1">
         <v>58</v>
       </c>
-      <c r="P15" s="1" t="s">
+      <c r="Q15" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="Q15" s="1" t="s">
+      <c r="R15" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="R15" s="1">
+      <c r="S15" s="1">
         <v>52</v>
       </c>
-      <c r="S15" s="1">
+      <c r="T15" s="1">
         <v>41.2</v>
       </c>
-      <c r="T15" s="1">
+      <c r="U15" s="1">
         <v>16.22</v>
       </c>
-      <c r="U15" s="1" t="s">
+      <c r="V15" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="V15" s="1">
+      <c r="W15" s="1">
         <v>52</v>
       </c>
-      <c r="W15" s="1">
+      <c r="X15" s="1">
         <v>37</v>
       </c>
-      <c r="X15" s="1">
+      <c r="Y15" s="1">
         <v>14.78</v>
       </c>
-      <c r="Y15" s="1" t="s">
+      <c r="Z15" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Z15" s="1" t="s">
+      <c r="AA15" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AA15" s="1" t="s">
+      <c r="AB15" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="AB15" s="1" t="s">
+      <c r="AC15" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:28" ht="27.6">
+    <row r="16" spans="1:29" ht="27.6">
       <c r="A16" s="1" t="s">
         <v>179</v>
       </c>
@@ -3515,70 +3605,73 @@
         <v>25</v>
       </c>
       <c r="H16" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="I16" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="I16" s="1">
+      <c r="J16" s="1">
         <v>2018</v>
       </c>
-      <c r="J16" s="1" t="s">
+      <c r="K16" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="K16" s="1">
+      <c r="L16" s="1">
         <v>40</v>
       </c>
-      <c r="L16" s="1" t="s">
+      <c r="M16" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="M16" s="1">
+      <c r="N16" s="1">
         <v>25.2</v>
       </c>
-      <c r="N16" s="1" t="s">
+      <c r="O16" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="O16" s="1">
+      <c r="P16" s="1">
         <v>50</v>
       </c>
-      <c r="P16" s="1" t="s">
+      <c r="Q16" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="Q16" s="1" t="s">
+      <c r="R16" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="R16" s="1">
+      <c r="S16" s="1">
         <v>20</v>
       </c>
-      <c r="S16" s="1">
+      <c r="T16" s="1">
         <v>89.33</v>
       </c>
-      <c r="T16" s="1">
+      <c r="U16" s="1">
         <v>10.94</v>
       </c>
-      <c r="U16" s="1" t="s">
+      <c r="V16" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="V16" s="1">
+      <c r="W16" s="1">
         <v>20</v>
       </c>
-      <c r="W16" s="1">
+      <c r="X16" s="1">
         <v>90.75</v>
       </c>
-      <c r="X16" s="1">
+      <c r="Y16" s="1">
         <v>9.35</v>
       </c>
-      <c r="Y16" s="1" t="s">
+      <c r="Z16" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="Z16" s="1" t="s">
+      <c r="AA16" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AA16" s="1" t="s">
+      <c r="AB16" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="AB16" s="1" t="s">
+      <c r="AC16" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="17" spans="1:28" ht="41.4">
+    <row r="17" spans="1:29" ht="41.4">
       <c r="A17" s="1" t="s">
         <v>179</v>
       </c>
@@ -3601,68 +3694,71 @@
         <v>26</v>
       </c>
       <c r="H17" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="I17" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="I17" s="1">
+      <c r="J17" s="1">
         <v>2016</v>
       </c>
-      <c r="J17" s="1" t="s">
+      <c r="K17" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="K17" s="1">
+      <c r="L17" s="1">
         <v>16</v>
       </c>
-      <c r="L17" s="1" t="s">
+      <c r="M17" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="M17" s="1">
+      <c r="N17" s="1">
         <v>27.63</v>
       </c>
-      <c r="N17" s="1" t="s">
+      <c r="O17" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="O17" s="1"/>
-      <c r="P17" s="1" t="s">
+      <c r="P17" s="1"/>
+      <c r="Q17" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="Q17" s="1" t="s">
+      <c r="R17" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="R17" s="1">
+      <c r="S17" s="1">
         <v>5</v>
       </c>
-      <c r="S17" s="1">
+      <c r="T17" s="1">
         <v>1.23</v>
       </c>
-      <c r="T17" s="1">
+      <c r="U17" s="1">
         <v>1</v>
       </c>
-      <c r="U17" s="1" t="s">
+      <c r="V17" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="V17" s="1">
+      <c r="W17" s="1">
         <v>6</v>
       </c>
-      <c r="W17" s="1">
+      <c r="X17" s="1">
         <v>0.1</v>
       </c>
-      <c r="X17" s="1">
+      <c r="Y17" s="1">
         <v>0.52</v>
       </c>
-      <c r="Y17" s="1" t="s">
+      <c r="Z17" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="Z17" s="1" t="s">
+      <c r="AA17" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AA17" s="1" t="s">
+      <c r="AB17" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="AB17" s="1" t="s">
+      <c r="AC17" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:28" ht="27.6">
+    <row r="18" spans="1:29" ht="27.6">
       <c r="A18" s="1" t="s">
         <v>178</v>
       </c>
@@ -3685,70 +3781,73 @@
         <v>29</v>
       </c>
       <c r="H18" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="I18" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="I18" s="1">
+      <c r="J18" s="1">
         <v>2019</v>
       </c>
-      <c r="J18" s="1" t="s">
+      <c r="K18" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="K18" s="1">
+      <c r="L18" s="1">
         <v>34</v>
       </c>
-      <c r="L18" s="1" t="s">
+      <c r="M18" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="M18" s="1">
+      <c r="N18" s="1">
         <v>40</v>
       </c>
-      <c r="N18" s="1" t="s">
+      <c r="O18" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="O18" s="1">
+      <c r="P18" s="1">
         <v>50</v>
       </c>
-      <c r="P18" s="1" t="s">
+      <c r="Q18" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="Q18" s="1" t="s">
+      <c r="R18" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="R18" s="1">
+      <c r="S18" s="1">
         <v>34</v>
       </c>
-      <c r="S18" s="1">
+      <c r="T18" s="1">
         <v>67.099999999999994</v>
       </c>
-      <c r="T18" s="1">
+      <c r="U18" s="1">
         <v>12.2</v>
       </c>
-      <c r="U18" s="1" t="s">
+      <c r="V18" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="V18" s="1">
+      <c r="W18" s="1">
         <v>34</v>
       </c>
-      <c r="W18" s="1">
+      <c r="X18" s="1">
         <v>54.9</v>
       </c>
-      <c r="X18" s="1">
+      <c r="Y18" s="1">
         <v>14.39</v>
       </c>
-      <c r="Y18" s="1" t="s">
+      <c r="Z18" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Z18" s="1" t="s">
+      <c r="AA18" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AA18" s="1" t="s">
+      <c r="AB18" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="AB18" s="1" t="s">
+      <c r="AC18" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:28" ht="58.95" customHeight="1">
+    <row r="19" spans="1:29" ht="58.95" customHeight="1">
       <c r="A19" s="1" t="s">
         <v>181</v>
       </c>
@@ -3771,70 +3870,73 @@
         <v>31</v>
       </c>
       <c r="H19" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="I19" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="I19" s="1">
+      <c r="J19" s="1">
         <v>2023</v>
       </c>
-      <c r="J19" s="1" t="s">
+      <c r="K19" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="K19" s="1">
+      <c r="L19" s="1">
         <v>146</v>
       </c>
-      <c r="L19" s="1" t="s">
+      <c r="M19" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="M19" s="1">
+      <c r="N19" s="1">
         <v>36.92</v>
       </c>
-      <c r="N19" s="1" t="s">
+      <c r="O19" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="O19" s="1">
+      <c r="P19" s="1">
         <v>60</v>
       </c>
-      <c r="P19" s="1" t="s">
+      <c r="Q19" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="Q19" s="1" t="s">
+      <c r="R19" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="R19" s="1">
+      <c r="S19" s="1">
         <v>146</v>
       </c>
-      <c r="S19" s="1">
+      <c r="T19" s="1">
         <v>5.68</v>
       </c>
-      <c r="T19" s="1">
+      <c r="U19" s="1">
         <v>2.44</v>
       </c>
-      <c r="U19" s="1" t="s">
+      <c r="V19" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="V19" s="1">
+      <c r="W19" s="1">
         <v>146</v>
       </c>
-      <c r="W19" s="1">
+      <c r="X19" s="1">
         <v>5.39</v>
       </c>
-      <c r="X19" s="1">
+      <c r="Y19" s="1">
         <v>2.4700000000000002</v>
       </c>
-      <c r="Y19" s="1" t="s">
+      <c r="Z19" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Z19" s="1" t="s">
+      <c r="AA19" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AA19" s="1" t="s">
+      <c r="AB19" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="AB19" s="1" t="s">
+      <c r="AC19" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:28" ht="41.4">
+    <row r="20" spans="1:29" ht="41.4">
       <c r="A20" s="1" t="s">
         <v>181</v>
       </c>
@@ -3857,66 +3959,69 @@
         <v>32</v>
       </c>
       <c r="H20" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="I20" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="I20" s="1">
+      <c r="J20" s="1">
         <v>2023</v>
       </c>
-      <c r="J20" s="1" t="s">
+      <c r="K20" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="K20" s="1">
+      <c r="L20" s="1">
         <v>36</v>
       </c>
-      <c r="L20" s="1" t="s">
+      <c r="M20" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="M20" s="1"/>
-      <c r="N20" s="1" t="s">
+      <c r="N20" s="1"/>
+      <c r="O20" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="O20" s="1"/>
-      <c r="P20" s="1" t="s">
+      <c r="P20" s="1"/>
+      <c r="Q20" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="Q20" s="1" t="s">
+      <c r="R20" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="R20" s="1">
+      <c r="S20" s="1">
         <v>12</v>
       </c>
-      <c r="S20" s="1">
+      <c r="T20" s="1">
         <v>8.93</v>
       </c>
-      <c r="T20" s="1">
+      <c r="U20" s="1">
         <v>0.82</v>
       </c>
-      <c r="U20" s="1" t="s">
+      <c r="V20" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="V20" s="1">
+      <c r="W20" s="1">
         <v>12</v>
       </c>
-      <c r="W20" s="1">
+      <c r="X20" s="1">
         <v>9.07</v>
       </c>
-      <c r="X20" s="1">
+      <c r="Y20" s="1">
         <v>1</v>
       </c>
-      <c r="Y20" s="1" t="s">
+      <c r="Z20" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="Z20" s="1" t="s">
+      <c r="AA20" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AA20" s="1" t="s">
+      <c r="AB20" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="AB20" s="1" t="s">
+      <c r="AC20" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="21" spans="1:28" ht="41.4">
+    <row r="21" spans="1:29" ht="41.4">
       <c r="A21" s="1" t="s">
         <v>177</v>
       </c>
@@ -3939,68 +4044,71 @@
         <v>35</v>
       </c>
       <c r="H21" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="I21" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="I21" s="1">
+      <c r="J21" s="1">
         <v>2015</v>
       </c>
-      <c r="J21" s="1" t="s">
+      <c r="K21" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="K21" s="1">
+      <c r="L21" s="1">
         <v>89</v>
       </c>
-      <c r="L21" s="1" t="s">
+      <c r="M21" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="M21" s="1">
+      <c r="N21" s="1">
         <v>23.65</v>
       </c>
-      <c r="N21" s="1" t="s">
+      <c r="O21" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="O21" s="1">
+      <c r="P21" s="1">
         <v>51</v>
       </c>
-      <c r="P21" s="1" t="s">
+      <c r="Q21" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="Q21" s="1" t="s">
+      <c r="R21" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="R21" s="1">
+      <c r="S21" s="1">
         <v>21</v>
       </c>
-      <c r="S21" s="1">
+      <c r="T21" s="1">
         <v>4.54</v>
       </c>
-      <c r="T21" s="1">
+      <c r="U21" s="1">
         <v>0.6</v>
       </c>
-      <c r="U21" s="1" t="s">
+      <c r="V21" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="V21" s="1">
+      <c r="W21" s="1">
         <v>23</v>
       </c>
-      <c r="W21" s="1">
+      <c r="X21" s="1">
         <v>4.45</v>
       </c>
-      <c r="X21" s="1">
+      <c r="Y21" s="1">
         <v>0.62</v>
       </c>
-      <c r="Y21" s="1" t="s">
+      <c r="Z21" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Z21" s="1" t="s">
+      <c r="AA21" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="AA21" s="1" t="s">
+      <c r="AB21" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="AB21" s="1"/>
+      <c r="AC21" s="1"/>
     </row>
-    <row r="22" spans="1:28" ht="41.4">
+    <row r="22" spans="1:29" ht="41.4">
       <c r="A22" s="1" t="s">
         <v>180</v>
       </c>
@@ -4023,70 +4131,73 @@
         <v>36</v>
       </c>
       <c r="H22" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="I22" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="I22" s="1">
+      <c r="J22" s="1">
         <v>2024</v>
       </c>
-      <c r="J22" s="1" t="s">
+      <c r="K22" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="K22" s="1">
+      <c r="L22" s="1">
         <v>314</v>
       </c>
-      <c r="L22" s="1" t="s">
+      <c r="M22" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="M22" s="1">
+      <c r="N22" s="1">
         <v>26</v>
       </c>
-      <c r="N22" s="1" t="s">
+      <c r="O22" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="O22" s="1">
+      <c r="P22" s="1">
         <v>59</v>
       </c>
-      <c r="P22" s="1" t="s">
+      <c r="Q22" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="Q22" s="1" t="s">
+      <c r="R22" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="R22" s="1">
+      <c r="S22" s="1">
         <v>78</v>
       </c>
-      <c r="S22" s="1">
+      <c r="T22" s="1">
         <v>3.56</v>
       </c>
-      <c r="T22" s="1">
+      <c r="U22" s="1">
         <v>0.59</v>
       </c>
-      <c r="U22" s="1" t="s">
+      <c r="V22" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="V22" s="1">
+      <c r="W22" s="1">
         <v>78</v>
       </c>
-      <c r="W22" s="1">
+      <c r="X22" s="1">
         <v>3.3</v>
       </c>
-      <c r="X22" s="1">
+      <c r="Y22" s="1">
         <v>0.84</v>
       </c>
-      <c r="Y22" s="1" t="s">
+      <c r="Z22" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Z22" s="1" t="s">
+      <c r="AA22" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AA22" s="1" t="s">
+      <c r="AB22" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="AB22" s="1" t="s">
+      <c r="AC22" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="23" spans="1:28" ht="34.200000000000003" customHeight="1">
+    <row r="23" spans="1:29" ht="34.200000000000003" customHeight="1">
       <c r="A23" s="1" t="s">
         <v>179</v>
       </c>
@@ -4109,68 +4220,71 @@
         <v>38</v>
       </c>
       <c r="H23" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="I23" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="I23" s="1">
+      <c r="J23" s="1">
         <v>2019</v>
       </c>
-      <c r="J23" s="1" t="s">
+      <c r="K23" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="K23" s="1">
+      <c r="L23" s="1">
         <v>20</v>
       </c>
-      <c r="L23" s="1" t="s">
+      <c r="M23" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="M23" s="1">
+      <c r="N23" s="1">
         <v>27</v>
       </c>
-      <c r="N23" s="1" t="s">
+      <c r="O23" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="O23" s="1">
+      <c r="P23" s="1">
         <v>35</v>
       </c>
-      <c r="P23" s="1" t="s">
+      <c r="Q23" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="Q23" s="1" t="s">
+      <c r="R23" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="R23" s="1">
+      <c r="S23" s="1">
         <v>20</v>
       </c>
-      <c r="S23" s="1">
+      <c r="T23" s="1">
         <v>3.8</v>
       </c>
-      <c r="T23" s="1">
+      <c r="U23" s="1">
         <v>1.3</v>
       </c>
-      <c r="U23" s="1" t="s">
+      <c r="V23" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="V23" s="1">
+      <c r="W23" s="1">
         <v>20</v>
       </c>
-      <c r="W23" s="1">
+      <c r="X23" s="1">
         <v>4.8</v>
       </c>
-      <c r="X23" s="1">
+      <c r="Y23" s="1">
         <v>1.1000000000000001</v>
       </c>
-      <c r="Y23" s="1" t="s">
+      <c r="Z23" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Z23" s="1" t="s">
+      <c r="AA23" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="AA23" s="1" t="s">
+      <c r="AB23" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="AB23" s="1"/>
+      <c r="AC23" s="1"/>
     </row>
-    <row r="24" spans="1:28" ht="41.4">
+    <row r="24" spans="1:29" ht="41.4">
       <c r="A24" s="1" t="s">
         <v>175</v>
       </c>
@@ -4192,69 +4306,72 @@
       <c r="G24" s="1">
         <v>39</v>
       </c>
-      <c r="H24" s="3" t="s">
+      <c r="H24" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="I24" s="1">
+      <c r="J24" s="1">
         <v>2020</v>
       </c>
-      <c r="J24" s="1" t="s">
+      <c r="K24" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="K24" s="1">
+      <c r="L24" s="1">
         <v>8</v>
       </c>
-      <c r="L24" s="1" t="s">
+      <c r="M24" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="M24" s="1"/>
-      <c r="N24" s="1" t="s">
+      <c r="N24" s="1"/>
+      <c r="O24" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="O24" s="1">
+      <c r="P24" s="1">
         <v>50</v>
       </c>
-      <c r="P24" s="1" t="s">
+      <c r="Q24" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="Q24" s="1" t="s">
+      <c r="R24" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="R24" s="1">
+      <c r="S24" s="1">
         <v>8</v>
       </c>
-      <c r="S24" s="1">
+      <c r="T24" s="1">
         <v>4</v>
       </c>
-      <c r="T24" s="1">
+      <c r="U24" s="1">
         <v>0.8</v>
       </c>
-      <c r="U24" s="1" t="s">
+      <c r="V24" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="V24" s="1">
+      <c r="W24" s="1">
         <v>8</v>
       </c>
-      <c r="W24" s="1">
+      <c r="X24" s="1">
         <v>3</v>
       </c>
-      <c r="X24" s="1">
+      <c r="Y24" s="1">
         <v>0.79</v>
       </c>
-      <c r="Y24" s="1" t="s">
+      <c r="Z24" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Z24" s="1" t="s">
+      <c r="AA24" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AA24" s="1" t="s">
+      <c r="AB24" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="AB24" s="1" t="s">
+      <c r="AC24" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:28" ht="27.6">
+    <row r="25" spans="1:29" ht="27.6">
       <c r="A25" s="1" t="s">
         <v>179</v>
       </c>
@@ -4277,70 +4394,73 @@
         <v>40</v>
       </c>
       <c r="H25" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="I25" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="I25" s="1">
+      <c r="J25" s="1">
         <v>2024</v>
       </c>
-      <c r="J25" s="1" t="s">
+      <c r="K25" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="K25" s="1">
+      <c r="L25" s="1">
         <v>14</v>
       </c>
-      <c r="L25" s="1" t="s">
+      <c r="M25" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="M25" s="1">
+      <c r="N25" s="1">
         <v>60.07</v>
       </c>
-      <c r="N25" s="1" t="s">
+      <c r="O25" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="O25" s="1">
+      <c r="P25" s="1">
         <v>50</v>
       </c>
-      <c r="P25" s="1" t="s">
+      <c r="Q25" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="Q25" s="1" t="s">
+      <c r="R25" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="R25" s="1">
+      <c r="S25" s="1">
         <v>14</v>
       </c>
-      <c r="S25" s="1">
+      <c r="T25" s="1">
         <v>3.89</v>
       </c>
-      <c r="T25" s="1">
+      <c r="U25" s="1">
         <v>1.29</v>
       </c>
-      <c r="U25" s="1" t="s">
+      <c r="V25" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="V25" s="1">
+      <c r="W25" s="1">
         <v>14</v>
       </c>
-      <c r="W25" s="1">
+      <c r="X25" s="1">
         <v>4</v>
       </c>
-      <c r="X25" s="1">
+      <c r="Y25" s="1">
         <v>1.29</v>
       </c>
-      <c r="Y25" s="1" t="s">
+      <c r="Z25" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Z25" s="1" t="s">
+      <c r="AA25" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AA25" s="1" t="s">
+      <c r="AB25" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="AB25" s="1" t="s">
+      <c r="AC25" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="1:28" ht="27.6">
+    <row r="26" spans="1:29" ht="27.6">
       <c r="A26" s="1" t="s">
         <v>122</v>
       </c>
@@ -4363,68 +4483,71 @@
         <v>41</v>
       </c>
       <c r="H26" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="I26" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="I26" s="1">
+      <c r="J26" s="1">
         <v>2023</v>
       </c>
-      <c r="J26" s="1" t="s">
+      <c r="K26" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="K26" s="1">
+      <c r="L26" s="1">
         <v>20</v>
       </c>
-      <c r="L26" s="1" t="s">
+      <c r="M26" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="M26" s="1">
+      <c r="N26" s="1">
         <v>24.3</v>
       </c>
-      <c r="N26" s="1" t="s">
+      <c r="O26" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="O26" s="1">
+      <c r="P26" s="1">
         <v>30</v>
       </c>
-      <c r="P26" s="1" t="s">
+      <c r="Q26" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="Q26" s="1" t="s">
+      <c r="R26" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="R26" s="1">
+      <c r="S26" s="1">
         <v>20</v>
       </c>
-      <c r="S26" s="1">
+      <c r="T26" s="1">
         <v>5.55</v>
       </c>
-      <c r="T26" s="1">
+      <c r="U26" s="1">
         <v>1.3</v>
       </c>
-      <c r="U26" s="1" t="s">
+      <c r="V26" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="V26" s="1">
+      <c r="W26" s="1">
         <v>20</v>
       </c>
-      <c r="W26" s="1">
+      <c r="X26" s="1">
         <v>4.95</v>
       </c>
-      <c r="X26" s="1">
+      <c r="Y26" s="1">
         <v>1.39</v>
       </c>
-      <c r="Y26" s="1"/>
-      <c r="Z26" s="1" t="s">
+      <c r="Z26" s="1"/>
+      <c r="AA26" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AA26" s="1" t="s">
+      <c r="AB26" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="AB26" s="1" t="s">
+      <c r="AC26" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:28" ht="38.4" customHeight="1">
+    <row r="27" spans="1:29" ht="38.4" customHeight="1">
       <c r="A27" s="1" t="s">
         <v>183</v>
       </c>
@@ -4447,70 +4570,73 @@
         <v>42</v>
       </c>
       <c r="H27" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="I27" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="I27" s="1">
+      <c r="J27" s="1">
         <v>2018</v>
       </c>
-      <c r="J27" s="1" t="s">
+      <c r="K27" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="K27" s="1">
+      <c r="L27" s="1">
         <v>39</v>
       </c>
-      <c r="L27" s="1" t="s">
+      <c r="M27" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="M27" s="1">
+      <c r="N27" s="1">
         <v>27.21</v>
       </c>
-      <c r="N27" s="1" t="s">
+      <c r="O27" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="O27" s="1">
+      <c r="P27" s="1">
         <v>38</v>
       </c>
-      <c r="P27" s="1" t="s">
+      <c r="Q27" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="Q27" s="1" t="s">
+      <c r="R27" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="R27" s="1">
+      <c r="S27" s="1">
         <v>19</v>
       </c>
-      <c r="S27" s="1">
+      <c r="T27" s="1">
         <v>0.66</v>
       </c>
-      <c r="T27" s="1">
+      <c r="U27" s="1">
         <v>0.48</v>
       </c>
-      <c r="U27" s="1" t="s">
+      <c r="V27" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="V27" s="1">
+      <c r="W27" s="1">
         <v>20</v>
       </c>
-      <c r="W27" s="1">
+      <c r="X27" s="1">
         <v>0.2</v>
       </c>
-      <c r="X27" s="1">
+      <c r="Y27" s="1">
         <v>0.85</v>
       </c>
-      <c r="Y27" s="1" t="s">
+      <c r="Z27" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Z27" s="1" t="s">
+      <c r="AA27" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AA27" s="1" t="s">
+      <c r="AB27" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="AB27" s="1" t="s">
+      <c r="AC27" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:28" ht="27.6">
+    <row r="28" spans="1:29" ht="27.6">
       <c r="A28" s="1" t="s">
         <v>201</v>
       </c>
@@ -4533,70 +4659,73 @@
         <v>45</v>
       </c>
       <c r="H28" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="I28" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="I28" s="1">
+      <c r="J28" s="1">
         <v>2025</v>
       </c>
-      <c r="J28" s="1" t="s">
+      <c r="K28" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="K28" s="1">
+      <c r="L28" s="1">
         <v>24</v>
       </c>
-      <c r="L28" s="1" t="s">
+      <c r="M28" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="M28" s="1">
+      <c r="N28" s="1">
         <v>27.5</v>
       </c>
-      <c r="N28" s="1" t="s">
+      <c r="O28" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="O28" s="1">
+      <c r="P28" s="1">
         <v>38</v>
       </c>
-      <c r="P28" s="1" t="s">
+      <c r="Q28" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="Q28" s="1" t="s">
+      <c r="R28" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="R28" s="1">
+      <c r="S28" s="1">
         <v>24</v>
       </c>
-      <c r="S28" s="1">
+      <c r="T28" s="1">
         <v>6.08</v>
       </c>
-      <c r="T28" s="1">
+      <c r="U28" s="1">
         <v>0.5</v>
       </c>
-      <c r="U28" s="1" t="s">
+      <c r="V28" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="V28" s="1">
+      <c r="W28" s="1">
         <v>24</v>
       </c>
-      <c r="W28" s="1">
+      <c r="X28" s="1">
         <v>5.95</v>
       </c>
-      <c r="X28" s="1">
+      <c r="Y28" s="1">
         <v>0.55000000000000004</v>
       </c>
-      <c r="Y28" s="1" t="s">
+      <c r="Z28" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="Z28" s="1" t="s">
+      <c r="AA28" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AA28" s="1" t="s">
+      <c r="AB28" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="AB28" s="1" t="s">
+      <c r="AC28" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="29" spans="1:28" ht="55.2">
+    <row r="29" spans="1:29" ht="55.2">
       <c r="A29" s="1" t="s">
         <v>187</v>
       </c>
@@ -4619,70 +4748,73 @@
         <v>47</v>
       </c>
       <c r="H29" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="I29" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="I29" s="1">
+      <c r="J29" s="1">
         <v>2018</v>
       </c>
-      <c r="J29" s="1" t="s">
+      <c r="K29" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="K29" s="1">
+      <c r="L29" s="1">
         <v>57</v>
       </c>
-      <c r="L29" s="1" t="s">
+      <c r="M29" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="M29" s="1">
+      <c r="N29" s="1">
         <v>24.5</v>
       </c>
-      <c r="N29" s="1" t="s">
+      <c r="O29" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="O29" s="1">
+      <c r="P29" s="1">
         <v>23</v>
       </c>
-      <c r="P29" s="1" t="s">
+      <c r="Q29" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="Q29" s="1" t="s">
+      <c r="R29" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="R29" s="1">
+      <c r="S29" s="1">
         <v>31</v>
       </c>
-      <c r="S29" s="1">
+      <c r="T29" s="1">
         <v>4.45</v>
       </c>
-      <c r="T29" s="1">
+      <c r="U29" s="1">
         <v>1.26</v>
       </c>
-      <c r="U29" s="1" t="s">
+      <c r="V29" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="V29" s="1">
+      <c r="W29" s="1">
         <v>26</v>
       </c>
-      <c r="W29" s="1">
+      <c r="X29" s="1">
         <v>3.7</v>
       </c>
-      <c r="X29" s="1">
+      <c r="Y29" s="1">
         <v>1.43</v>
       </c>
-      <c r="Y29" s="1" t="s">
+      <c r="Z29" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="Z29" s="1" t="s">
+      <c r="AA29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AA29" s="1" t="s">
+      <c r="AB29" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="AB29" s="1" t="s">
+      <c r="AC29" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="30" spans="1:28" ht="41.4">
+    <row r="30" spans="1:29" ht="41.4">
       <c r="A30" s="1" t="s">
         <v>179</v>
       </c>
@@ -4705,70 +4837,73 @@
         <v>48</v>
       </c>
       <c r="H30" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="I30" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="I30" s="1">
+      <c r="J30" s="1">
         <v>2016</v>
       </c>
-      <c r="J30" s="1" t="s">
+      <c r="K30" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="K30" s="1">
+      <c r="L30" s="1">
         <v>32</v>
       </c>
-      <c r="L30" s="1" t="s">
+      <c r="M30" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="M30" s="1">
+      <c r="N30" s="1">
         <v>23.31</v>
       </c>
-      <c r="N30" s="1" t="s">
+      <c r="O30" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="O30" s="1">
+      <c r="P30" s="1">
         <v>41</v>
       </c>
-      <c r="P30" s="1" t="s">
+      <c r="Q30" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="Q30" s="1" t="s">
+      <c r="R30" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="R30" s="1">
+      <c r="S30" s="1">
         <v>32</v>
       </c>
-      <c r="S30" s="1">
+      <c r="T30" s="1">
         <v>4.54</v>
       </c>
-      <c r="T30" s="1">
+      <c r="U30" s="1">
         <v>1.01</v>
       </c>
-      <c r="U30" s="1" t="s">
+      <c r="V30" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="V30" s="1">
+      <c r="W30" s="1">
         <v>32</v>
       </c>
-      <c r="W30" s="1">
+      <c r="X30" s="1">
         <v>5.0999999999999996</v>
       </c>
-      <c r="X30" s="1">
+      <c r="Y30" s="1">
         <v>0.98</v>
       </c>
-      <c r="Y30" s="1" t="s">
+      <c r="Z30" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="Z30" s="1" t="s">
+      <c r="AA30" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AA30" s="1" t="s">
+      <c r="AB30" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="AB30" s="1" t="s">
+      <c r="AC30" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="31" spans="1:28" ht="27.6">
+    <row r="31" spans="1:29" ht="27.6">
       <c r="A31" s="1" t="s">
         <v>175</v>
       </c>
@@ -4790,63 +4925,66 @@
       <c r="G31" s="1">
         <v>51</v>
       </c>
-      <c r="H31" s="6" t="s">
+      <c r="H31" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="I31" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="I31" s="1">
+      <c r="J31" s="1">
         <v>2023</v>
       </c>
-      <c r="J31" s="1" t="s">
+      <c r="K31" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="K31" s="1">
+      <c r="L31" s="1">
         <v>60</v>
       </c>
-      <c r="L31" s="1"/>
       <c r="M31" s="1"/>
       <c r="N31" s="1"/>
       <c r="O31" s="1"/>
-      <c r="P31" s="1" t="s">
+      <c r="P31" s="1"/>
+      <c r="Q31" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="Q31" s="1" t="s">
+      <c r="R31" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="R31" s="1">
+      <c r="S31" s="1">
         <v>60</v>
       </c>
-      <c r="S31" s="1">
+      <c r="T31" s="1">
         <v>5.18</v>
       </c>
-      <c r="T31" s="1">
+      <c r="U31" s="1">
         <v>1.63</v>
       </c>
-      <c r="U31" s="1" t="s">
+      <c r="V31" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="V31" s="1">
+      <c r="W31" s="1">
         <v>60</v>
       </c>
-      <c r="W31" s="1">
+      <c r="X31" s="1">
         <v>4.7</v>
       </c>
-      <c r="X31" s="1">
+      <c r="Y31" s="1">
         <v>1.87</v>
       </c>
-      <c r="Y31" s="1" t="s">
+      <c r="Z31" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="Z31" s="1" t="s">
+      <c r="AA31" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AA31" s="1" t="s">
+      <c r="AB31" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="AB31" s="1" t="s">
+      <c r="AC31" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="1:28" ht="96.6">
+    <row r="32" spans="1:29" ht="96.6">
       <c r="A32" s="1" t="s">
         <v>122</v>
       </c>
@@ -4869,68 +5007,71 @@
         <v>60</v>
       </c>
       <c r="H32" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="I32" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="I32" s="1">
+      <c r="J32" s="1">
         <v>2021</v>
       </c>
-      <c r="J32" s="1" t="s">
+      <c r="K32" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="K32" s="1">
+      <c r="L32" s="1">
         <v>10</v>
       </c>
-      <c r="L32" s="1" t="s">
+      <c r="M32" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="M32" s="1">
+      <c r="N32" s="1">
         <v>26.36</v>
       </c>
-      <c r="N32" s="1" t="s">
+      <c r="O32" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="O32" s="1">
+      <c r="P32" s="1">
         <v>60</v>
       </c>
-      <c r="P32" s="1" t="s">
+      <c r="Q32" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="Q32" s="1" t="s">
+      <c r="R32" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="R32" s="1">
+      <c r="S32" s="1">
         <v>10</v>
       </c>
-      <c r="S32" s="4">
+      <c r="T32" s="4">
         <v>4.0999999999999996</v>
       </c>
-      <c r="T32" s="4">
+      <c r="U32" s="4">
         <v>0.32500000000000001</v>
       </c>
-      <c r="U32" s="1" t="s">
+      <c r="V32" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="V32" s="4">
+      <c r="W32" s="4">
         <v>10</v>
       </c>
-      <c r="W32" s="4">
+      <c r="X32" s="4">
         <v>5.3</v>
       </c>
-      <c r="X32" s="4">
+      <c r="Y32" s="4">
         <v>0.33</v>
       </c>
-      <c r="Y32" s="1" t="s">
+      <c r="Z32" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="Z32" s="1" t="s">
+      <c r="AA32" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="AA32" s="1" t="s">
+      <c r="AB32" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="AB32" s="1"/>
+      <c r="AC32" s="1"/>
     </row>
-    <row r="33" spans="1:28" ht="69">
+    <row r="33" spans="1:29" ht="69">
       <c r="A33" s="1" t="s">
         <v>179</v>
       </c>
@@ -4952,71 +5093,74 @@
       <c r="G33" s="1">
         <v>64</v>
       </c>
-      <c r="H33" s="3" t="s">
+      <c r="H33" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="I33" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="I33" s="1">
+      <c r="J33" s="1">
         <v>2021</v>
       </c>
-      <c r="J33" s="1" t="s">
+      <c r="K33" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="K33" s="1">
+      <c r="L33" s="1">
         <v>23</v>
       </c>
-      <c r="L33" s="1" t="s">
+      <c r="M33" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="M33" s="1">
+      <c r="N33" s="1">
         <v>25.13</v>
       </c>
-      <c r="N33" s="1" t="s">
+      <c r="O33" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="O33" s="1">
+      <c r="P33" s="1">
         <v>65</v>
       </c>
-      <c r="P33" s="1" t="s">
+      <c r="Q33" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="Q33" s="1" t="s">
+      <c r="R33" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="R33" s="1">
+      <c r="S33" s="1">
         <v>23</v>
       </c>
-      <c r="S33" s="1">
+      <c r="T33" s="1">
         <v>3.1</v>
       </c>
-      <c r="T33" s="1">
+      <c r="U33" s="1">
         <v>0.79</v>
       </c>
-      <c r="U33" s="1" t="s">
+      <c r="V33" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="V33" s="1">
+      <c r="W33" s="1">
         <v>23</v>
       </c>
-      <c r="W33" s="1">
+      <c r="X33" s="1">
         <v>2.91</v>
       </c>
-      <c r="X33" s="1">
+      <c r="Y33" s="1">
         <v>0.86</v>
       </c>
-      <c r="Y33" s="1" t="s">
+      <c r="Z33" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="Z33" s="1" t="s">
+      <c r="AA33" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AA33" s="1" t="s">
+      <c r="AB33" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="AB33" s="1" t="s">
+      <c r="AC33" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="34" spans="1:28" ht="69">
+    <row r="34" spans="1:29" ht="69">
       <c r="A34" s="1" t="s">
         <v>175</v>
       </c>
@@ -5039,70 +5183,73 @@
         <v>68</v>
       </c>
       <c r="H34" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="I34" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="I34" s="1">
+      <c r="J34" s="1">
         <v>2022</v>
       </c>
-      <c r="J34" s="1" t="s">
+      <c r="K34" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="K34" s="1">
+      <c r="L34" s="1">
         <v>30</v>
       </c>
-      <c r="L34" s="1" t="s">
+      <c r="M34" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="M34" s="1">
+      <c r="N34" s="1">
         <v>26.03</v>
       </c>
-      <c r="N34" s="1" t="s">
+      <c r="O34" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="O34" s="1">
+      <c r="P34" s="1">
         <v>47</v>
       </c>
-      <c r="P34" s="1" t="s">
+      <c r="Q34" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="Q34" s="1" t="s">
+      <c r="R34" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="R34" s="1">
+      <c r="S34" s="1">
         <v>10</v>
       </c>
-      <c r="S34" s="1">
+      <c r="T34" s="1">
         <v>5.33</v>
       </c>
-      <c r="T34" s="1">
+      <c r="U34" s="1">
         <v>1.1399999999999999</v>
       </c>
-      <c r="U34" s="1" t="s">
+      <c r="V34" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="V34" s="1">
+      <c r="W34" s="1">
         <v>10</v>
       </c>
-      <c r="W34" s="1">
+      <c r="X34" s="1">
         <v>4.6399999999999997</v>
       </c>
-      <c r="X34" s="1">
+      <c r="Y34" s="1">
         <v>0.7</v>
       </c>
-      <c r="Y34" s="1" t="s">
+      <c r="Z34" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="Z34" s="1" t="s">
+      <c r="AA34" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AA34" s="1" t="s">
+      <c r="AB34" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="AB34" s="1" t="s">
+      <c r="AC34" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="35" spans="1:28" ht="27.6">
+    <row r="35" spans="1:29" ht="27.6">
       <c r="A35" s="1" t="s">
         <v>182</v>
       </c>
@@ -5122,65 +5269,66 @@
       <c r="G35" s="1">
         <v>69</v>
       </c>
-      <c r="H35" s="1" t="s">
+      <c r="H35" s="1"/>
+      <c r="I35" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="I35" s="1">
+      <c r="J35" s="1">
         <v>2024</v>
       </c>
-      <c r="J35" s="1" t="s">
+      <c r="K35" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="K35" s="1">
+      <c r="L35" s="1">
         <v>10</v>
       </c>
-      <c r="L35" s="1" t="s">
+      <c r="M35" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="M35" s="1"/>
-      <c r="N35" s="1" t="s">
+      <c r="N35" s="1"/>
+      <c r="O35" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="O35" s="1">
+      <c r="P35" s="1">
         <v>60</v>
       </c>
-      <c r="P35" s="1" t="s">
+      <c r="Q35" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="Q35" s="1" t="s">
+      <c r="R35" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="R35" s="1">
+      <c r="S35" s="1">
         <v>10</v>
       </c>
-      <c r="S35" s="1">
+      <c r="T35" s="1">
         <v>4.6100000000000003</v>
       </c>
-      <c r="T35" s="1">
+      <c r="U35" s="1">
         <v>1.37</v>
       </c>
-      <c r="U35" s="1" t="s">
+      <c r="V35" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="V35" s="1">
+      <c r="W35" s="1">
         <v>10</v>
       </c>
-      <c r="W35" s="1">
+      <c r="X35" s="1">
         <v>4.1399999999999997</v>
       </c>
-      <c r="X35" s="1">
+      <c r="Y35" s="1">
         <v>1.41</v>
       </c>
-      <c r="Y35" s="1" t="s">
+      <c r="Z35" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Z35" s="1" t="s">
+      <c r="AA35" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="AA35" s="1" t="s">
+      <c r="AB35" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="AB35" s="1"/>
+      <c r="AC35" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -5201,15 +5349,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A5413AB96661EC46B3846FFEFBACC949" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="6aebf314c5b66d064d8fbfb0809e7bc2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="c75ec144-b9ff-4135-afbf-fbc38a6fd8b9" xmlns:ns4="e29641a7-d149-4a2d-8344-ad39683b5976" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4ea25234db497c6722af7ba3b054603e" ns3:_="" ns4:_="">
     <xsd:import namespace="c75ec144-b9ff-4135-afbf-fbc38a6fd8b9"/>
@@ -5436,6 +5575,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F9E61951-B539-4B2A-A33D-75308358C4C9}">
   <ds:schemaRefs>
@@ -5454,14 +5602,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C7666DB1-BE27-42CB-83CA-028248B221FF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7D45A603-5BC0-40EB-A08C-3C9AD74DCD89}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5478,4 +5618,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C7666DB1-BE27-42CB-83CA-028248B221FF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>